--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:27:05+00:00</t>
+    <t>2023-06-08T09:38:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dr-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$203</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6581" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6614" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:38:17+00:00</t>
+    <t>2023-06-08T10:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2019,6 +2019,21 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
+  </si>
+  <si>
+    <t>typeDiplome</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
@@ -2376,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ202"/>
+  <dimension ref="A1:AJ203"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.60546875" customWidth="true" bestFit="true"/>
@@ -10929,7 +10944,7 @@
         <v>90</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -22777,9 +22792,11 @@
         <v>648</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C199" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="D199" t="s" s="2">
         <v>71</v>
       </c>
@@ -22788,10 +22805,10 @@
         <v>72</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>71</v>
@@ -22800,19 +22817,19 @@
         <v>79</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>277</v>
+        <v>650</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>279</v>
+        <v>651</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>71</v>
@@ -22837,13 +22854,11 @@
         <v>71</v>
       </c>
       <c r="X199" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>71</v>
+        <v>652</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>71</v>
@@ -22861,13 +22876,13 @@
         <v>71</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>90</v>
@@ -22878,10 +22893,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22901,22 +22916,22 @@
         <v>71</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>296</v>
+        <v>92</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>650</v>
+        <v>277</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>651</v>
+        <v>278</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>652</v>
+        <v>280</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>71</v>
@@ -22965,7 +22980,7 @@
         <v>71</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>649</v>
+        <v>281</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>72</v>
@@ -22977,15 +22992,15 @@
         <v>90</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>301</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -23008,18 +23023,20 @@
         <v>71</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O201" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O201" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P201" t="s" s="2">
         <v>71</v>
       </c>
@@ -23067,7 +23084,7 @@
         <v>71</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>72</v>
@@ -23079,15 +23096,15 @@
         <v>90</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -23098,10 +23115,10 @@
         <v>72</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>71</v>
@@ -23110,7 +23127,7 @@
         <v>71</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>658</v>
+        <v>303</v>
       </c>
       <c r="L202" t="s" s="2">
         <v>659</v>
@@ -23121,9 +23138,7 @@
       <c r="N202" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="O202" t="s" s="2">
-        <v>662</v>
-      </c>
+      <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
         <v>71</v>
       </c>
@@ -23147,11 +23162,13 @@
         <v>71</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y202" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="Z202" t="s" s="2">
-        <v>663</v>
+        <v>71</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>71</v>
@@ -23169,23 +23186,125 @@
         <v>71</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ202" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="203" hidden="true">
+      <c r="A203" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C203" s="2"/>
+      <c r="D203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G203" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H203" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K203" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L203" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O203" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="P203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q203" s="2"/>
+      <c r="R203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X203" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y203" s="2"/>
+      <c r="Z203" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AA203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE203" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF203" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AG203" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH203" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI203" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ203" t="s" s="2">
         <v>117</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ202">
+  <autoFilter ref="A1:AJ203">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -23195,7 +23314,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI201">
+  <conditionalFormatting sqref="A2:AI202">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
